--- a/y12310/data/samples/示例数据.xlsx
+++ b/y12310/data/samples/示例数据.xlsx
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46175.69810657363</v>
+        <v>46176.79850732438</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>46175.69810657363</v>
+        <v>46176.79850732438</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46175.69810657363</v>
+        <v>46176.79850732438</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46176.69810657363</v>
+        <v>46177.79850732438</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46176.69810657363</v>
+        <v>46177.79850732438</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46175.19810657363</v>
+        <v>46176.29850732438</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46175.69810657363</v>
+        <v>46176.79850732438</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46175.69810657363</v>
+        <v>46176.79850732438</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46175.69810657363</v>
+        <v>46176.79850732438</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>46175.69810657363</v>
+        <v>46176.79850732438</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>46175.69810657363</v>
+        <v>46176.79850732438</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>

--- a/y12310/data/samples/示例数据.xlsx
+++ b/y12310/data/samples/示例数据.xlsx
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46176.79850732438</v>
+        <v>46176.81244577694</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>46176.79850732438</v>
+        <v>46176.81244577694</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46176.79850732438</v>
+        <v>46176.81244577694</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46177.79850732438</v>
+        <v>46177.81244577694</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46177.79850732438</v>
+        <v>46177.81244577694</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46176.29850732438</v>
+        <v>46176.31244577694</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46176.79850732438</v>
+        <v>46176.81244577694</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46176.79850732438</v>
+        <v>46176.81244577694</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46176.79850732438</v>
+        <v>46176.81244577694</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>46176.79850732438</v>
+        <v>46176.81244577694</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>46176.79850732438</v>
+        <v>46176.81244577694</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>

--- a/y12310/data/samples/示例数据.xlsx
+++ b/y12310/data/samples/示例数据.xlsx
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46176.81244577694</v>
+        <v>46177.11212831668</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>46176.81244577694</v>
+        <v>46177.11212831668</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46176.81244577694</v>
+        <v>46177.11212831668</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46177.81244577694</v>
+        <v>46178.11212831668</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46177.81244577694</v>
+        <v>46178.11212831668</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46176.31244577694</v>
+        <v>46176.61212831668</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46176.81244577694</v>
+        <v>46177.11212831668</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46176.81244577694</v>
+        <v>46177.11212831668</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46176.81244577694</v>
+        <v>46177.11212831668</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>46176.81244577694</v>
+        <v>46177.11212831668</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>46176.81244577694</v>
+        <v>46177.11212831668</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>

--- a/y12310/data/samples/示例数据.xlsx
+++ b/y12310/data/samples/示例数据.xlsx
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46177.11212831668</v>
+        <v>46177.1289392726</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>46177.11212831668</v>
+        <v>46177.1289392726</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46177.11212831668</v>
+        <v>46177.1289392726</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46178.11212831668</v>
+        <v>46178.1289392726</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46178.11212831668</v>
+        <v>46178.1289392726</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46176.61212831668</v>
+        <v>46176.6289392726</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46177.11212831668</v>
+        <v>46177.1289392726</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46177.11212831668</v>
+        <v>46177.1289392726</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46177.11212831668</v>
+        <v>46177.1289392726</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>46177.11212831668</v>
+        <v>46177.1289392726</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>46177.11212831668</v>
+        <v>46177.1289392726</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
